--- a/output/laminas_comunales/comunal_o_ocup_a_2019_nuble.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C2">
-        <v>38.3897476196289</v>
+        <v>58.9575691223145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C3">
-        <v>37.1622200012207</v>
+        <v>57.7741584777832</v>
       </c>
     </row>
     <row r="4">
@@ -414,37 +414,37 @@
         </is>
       </c>
       <c r="C4">
-        <v>33.4414405822754</v>
+        <v>56.1449890136719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="C5">
-        <v>33.1451606750488</v>
+        <v>54.9677352905273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C6">
-        <v>32.9656066894531</v>
+        <v>53.932746887207</v>
       </c>
     </row>
     <row r="7">
@@ -459,22 +459,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>32.6797981262207</v>
+        <v>51.8758888244629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="C8">
-        <v>32.3992347717285</v>
+        <v>51.7838935852051</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>31.665828704834</v>
+        <v>51.7678909301758</v>
       </c>
     </row>
     <row r="10">
@@ -504,187 +504,2077 @@
         </is>
       </c>
       <c r="C10">
-        <v>31.6477737426758</v>
+        <v>51.3440322875977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="C11">
-        <v>30.9805755615234</v>
+        <v>50.5141830444336</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="C12">
-        <v>29.6167545318604</v>
+        <v>49.0606269836426</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="C13">
-        <v>29.4543170928955</v>
+        <v>47.9158782958984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ranquil</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C14">
-        <v>27.7149562835693</v>
+        <v>47.1162071228027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C15">
-        <v>26.7930335998535</v>
+        <v>47.0449066162109</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C16">
-        <v>26.4405975341797</v>
+        <v>46.3235702514649</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C17">
-        <v>25.8829116821289</v>
+        <v>46.319019317627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C18">
-        <v>25.2880764007568</v>
+        <v>46.1979827880859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C19">
-        <v>24.9670333862305</v>
+        <v>44.539176940918</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="C20">
-        <v>24.2182884216309</v>
+        <v>44.2794456481934</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C21">
-        <v>23.7901592254639</v>
+        <v>44.0164031982422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>43.5072135925293</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>43.155158996582</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>43.0442962646484</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>42.9527740478516</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>42.8603897094727</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>42.8435211181641</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>42.8129119873047</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>42.7862167358398</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>42.4535064697266</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>41.8886909484863</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>41.3092384338379</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>40.6814308166504</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>40.2066497802734</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>39.6464424133301</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>39.5874366760254</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>39.4445991516113</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>39.3158988952637</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>38.7967376708984</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38.5449409484863</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>38.5015335083008</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>38.3897476196289</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>16202</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Cobquecura</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C43">
+        <v>38.0882339477539</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>37.2470741271973</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>37.1622200012207</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>36.7999382019043</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>36.6935920715332</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>36.0401573181152</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>35.3995628356934</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>34.3594093322754</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>34.3334732055664</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>33.7977447509766</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>33.4414405822754</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>33.2812690734863</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.1451606750488</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>32.9656066894531</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>32.6797981262207</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>32.5705986022949</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>32.3992347717285</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>32.2681198120117</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>32.0774421691895</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>31.8315963745117</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>31.8175411224365</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>31.7983093261719</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>31.665828704834</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>31.6477737426758</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>31.4960632324219</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>31.3894195556641</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>31.3258380889893</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>31.3237361907959</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>31.3019390106201</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>31.1710796356201</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>31.0545825958252</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>31.0243492126465</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>31.0202960968018</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>30.9805755615234</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>30.782112121582</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>30.7042770385742</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>30.5057029724121</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>30.3255100250244</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>30.22705078125</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>30.0298023223877</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>29.924711227417</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>29.8017044067383</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>29.6167545318604</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>29.4543170928955</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>29.1745433807373</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>28.9452171325684</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>28.7764720916748</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>28.3273735046387</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>28.3129253387451</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>27.8182849884033</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>27.7149562835693</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>26.9372940063477</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>26.7930335998535</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>26.4405975341797</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>26.2307929992676</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>26.1205863952637</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>26.0087966918945</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>25.8829116821289</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>25.7846641540527</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>25.2880764007568</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>24.9670333862305</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>24.9462051391602</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>24.6790904998779</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>24.2182884216309</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>24.1054058074951</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>24.0361404418945</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>23.791618347168</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>23.7901592254639</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>23.231803894043</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>22.7842807769775</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>22.6702632904053</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>22.5528659820557</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>22.5330028533936</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>21.9119625091553</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C117">
         <v>21.5017070770264</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>20.4931163787842</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>20.1639919281006</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>20.1328105926514</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>19.9039669036865</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>19.7882308959961</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>19.4805641174316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>19.3231449127197</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>19.0248031616211</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>18.8024234771729</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>17.8039875030518</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>9.165114402771</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>8.939766883850099</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>8.674948692321779</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>8.49771308898926</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>7.42044878005981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>7.3858323097229</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>7.20460176467896</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>7.20260906219482</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>7.04203653335571</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>6.85552549362183</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>6.35342788696289</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>6.33210182189941</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>6.23044109344482</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>6.06204128265381</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>5.91931200027466</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>5.36779308319092</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>5.35899448394775</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>4.73865747451782</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>4.66049385070801</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>4.49879217147827</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>4.15691614151001</v>
       </c>
     </row>
   </sheetData>
